--- a/public/tagihan_excel.xlsx
+++ b/public/tagihan_excel.xlsx
@@ -18,6 +18,31 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>NAMA</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>KELAS</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>KELOMPOK</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ANGKATAN</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>NOMINAL</t>
         </is>
       </c>
@@ -28,7 +53,30 @@
           <t>3000001107</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Contoh Siswa 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MTQ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>2024</v>
+      </c>
+      <c r="G2">
         <v>500000</v>
       </c>
     </row>
@@ -38,7 +86,30 @@
           <t>3000001108</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Contoh Siswa 2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MTQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>2024</v>
+      </c>
+      <c r="G3">
         <v>500000</v>
       </c>
     </row>
